--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Immunization</t>
+    <t>This StructureDefinition contains the maps for VistA V IMMUNIZATION (file 9000010.11) to FHIR Immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1568,7 +1568,7 @@
     <t>.value</t>
   </si>
   <si>
-    <t>1621: reference from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
+    <t>++: reference from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
   </si>
   <si>
     <t>Immunization.reaction.reported</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -416,10 +416,7 @@
     <t>This is generally only used for the status of "not-done". The reason for performing the immunization event is captured in reasonCode, not here.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
+    <t>http://va.gov/fhir/ValueSet/VFimmunizationStatusReason</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -440,10 +437,7 @@
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
+    <t>http://va.gov/fhir/ValueSet/VFinferredCVX</t>
   </si>
   <si>
     <t xml:space="preserve">us-core-5
@@ -835,7 +829,7 @@
     <t>Immun.Immunization.ImmunizationInformationSourceIEN</t>
   </si>
   <si>
-    <t>607: terminologyMaps using VF_immunizationPrimarySource on V IMMUNIZATION - EVENT INFORMATION SOURCE (#9000010.11-1301)</t>
+    <t>607: transform using VF_immunizationPrimarySource on V IMMUNIZATION - EVENT INFORMATION SOURCE (#9000010.11-1301)</t>
   </si>
   <si>
     <t>Immunization.reportOrigin</t>
@@ -848,6 +842,9 @@
   </si>
   <si>
     <t>Should not be populated if primarySource = True, not required even if primarySource = False.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>The source of the data for a record which is not from a primary source.</t>
@@ -1208,6 +1205,9 @@
   </si>
   <si>
     <t>Describes the type of performance (e.g. ordering provider, administering provider, etc.).</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>The role a practitioner or organization plays in the immunization event.</t>
@@ -2015,7 +2015,7 @@
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="11.4375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3446,11 +3446,11 @@
         <v>35</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>35</v>
@@ -3483,13 +3483,13 @@
         <v>58</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>35</v>
@@ -3501,15 +3501,15 @@
         <v>120</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3535,10 +3535,10 @@
         <v>123</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3565,11 +3565,11 @@
         <v>35</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>35</v>
@@ -3587,7 +3587,7 @@
         <v>35</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>46</v>
@@ -3596,39 +3596,39 @@
         <v>46</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>58</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3651,13 +3651,13 @@
         <v>35</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3708,7 +3708,7 @@
         <v>35</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>36</v>
@@ -3729,7 +3729,7 @@
         <v>35</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>35</v>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3778,7 +3778,7 @@
         <v>93</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N15" t="s" s="2">
         <v>95</v>
@@ -3819,19 +3819,19 @@
         <v>35</v>
       </c>
       <c r="AB15" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE15" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AC15" t="s" s="2">
+      <c r="AF15" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>36</v>
@@ -3852,7 +3852,7 @@
         <v>35</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>35</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3895,19 +3895,19 @@
         <v>47</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>35</v>
@@ -3956,7 +3956,7 @@
         <v>35</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
@@ -3974,10 +3974,10 @@
         <v>35</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>35</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4020,13 +4020,13 @@
         <v>35</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4077,7 +4077,7 @@
         <v>35</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
@@ -4098,7 +4098,7 @@
         <v>35</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>35</v>
@@ -4115,10 +4115,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4147,7 +4147,7 @@
         <v>93</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>95</v>
@@ -4188,19 +4188,19 @@
         <v>35</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
@@ -4221,7 +4221,7 @@
         <v>35</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>35</v>
@@ -4238,10 +4238,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4267,16 +4267,16 @@
         <v>60</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>35</v>
@@ -4325,7 +4325,7 @@
         <v>35</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
@@ -4343,10 +4343,10 @@
         <v>35</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>35</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4389,16 +4389,16 @@
         <v>47</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4448,7 +4448,7 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
@@ -4466,10 +4466,10 @@
         <v>35</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>35</v>
@@ -4486,10 +4486,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4515,14 +4515,14 @@
         <v>66</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>35</v>
@@ -4571,7 +4571,7 @@
         <v>35</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -4589,30 +4589,30 @@
         <v>35</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AQ21" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4635,17 +4635,17 @@
         <v>47</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>35</v>
@@ -4694,7 +4694,7 @@
         <v>35</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -4712,10 +4712,10 @@
         <v>35</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>35</v>
@@ -4732,10 +4732,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4758,19 +4758,19 @@
         <v>47</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>35</v>
@@ -4819,7 +4819,7 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -4837,10 +4837,10 @@
         <v>35</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>35</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4883,19 +4883,19 @@
         <v>47</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>35</v>
@@ -4944,7 +4944,7 @@
         <v>35</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
@@ -4962,10 +4962,10 @@
         <v>35</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>35</v>
@@ -4982,14 +4982,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5008,13 +5008,13 @@
         <v>47</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5065,7 +5065,7 @@
         <v>35</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>46</v>
@@ -5080,33 +5080,33 @@
         <v>58</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5129,13 +5129,13 @@
         <v>35</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5186,7 +5186,7 @@
         <v>35</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
@@ -5201,16 +5201,16 @@
         <v>58</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>35</v>
@@ -5224,10 +5224,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5250,16 +5250,16 @@
         <v>47</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5297,17 +5297,17 @@
         <v>35</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>46</v>
@@ -5322,19 +5322,19 @@
         <v>58</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>35</v>
@@ -5345,13 +5345,13 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>35</v>
@@ -5373,16 +5373,16 @@
         <v>47</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5432,7 +5432,7 @@
         <v>35</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>46</v>
@@ -5447,33 +5447,33 @@
         <v>58</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AN28" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="AP28" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5496,13 +5496,13 @@
         <v>35</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5553,7 +5553,7 @@
         <v>35</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
@@ -5574,27 +5574,27 @@
         <v>35</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5617,16 +5617,16 @@
         <v>47</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5676,7 +5676,7 @@
         <v>35</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -5694,30 +5694,30 @@
         <v>35</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5743,13 +5743,13 @@
         <v>123</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5775,14 +5775,14 @@
         <v>35</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>269</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>35</v>
       </c>
@@ -5799,7 +5799,7 @@
         <v>35</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -5817,13 +5817,13 @@
         <v>35</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>35</v>
@@ -5837,10 +5837,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5863,13 +5863,13 @@
         <v>35</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5920,7 +5920,7 @@
         <v>35</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
@@ -5935,16 +5935,16 @@
         <v>58</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>35</v>
@@ -5958,10 +5958,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5984,13 +5984,13 @@
         <v>35</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6041,7 +6041,7 @@
         <v>35</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -6059,30 +6059,30 @@
         <v>35</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AN33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AQ33" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6105,13 +6105,13 @@
         <v>35</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6162,7 +6162,7 @@
         <v>35</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -6180,30 +6180,30 @@
         <v>35</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AN34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6226,13 +6226,13 @@
         <v>35</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -6301,10 +6301,10 @@
         <v>35</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>35</v>
@@ -6321,10 +6321,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6350,10 +6350,10 @@
         <v>123</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6380,14 +6380,14 @@
         <v>35</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>35</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>35</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -6422,16 +6422,16 @@
         <v>35</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>35</v>
@@ -6442,10 +6442,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6471,10 +6471,10 @@
         <v>123</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6501,14 +6501,14 @@
         <v>35</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>312</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>35</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>35</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -6543,16 +6543,16 @@
         <v>35</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>35</v>
@@ -6563,10 +6563,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6589,13 +6589,13 @@
         <v>35</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6646,7 +6646,7 @@
         <v>35</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -6664,30 +6664,30 @@
         <v>35</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AN38" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP38" t="s" s="2">
+      <c r="AQ38" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6710,13 +6710,13 @@
         <v>35</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6767,7 +6767,7 @@
         <v>35</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -6788,7 +6788,7 @@
         <v>35</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>35</v>
@@ -6805,10 +6805,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6837,7 +6837,7 @@
         <v>93</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>95</v>
@@ -6878,19 +6878,19 @@
         <v>35</v>
       </c>
       <c r="AB40" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE40" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AC40" t="s" s="2">
+      <c r="AF40" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
@@ -6911,7 +6911,7 @@
         <v>35</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>35</v>
@@ -6928,10 +6928,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6954,19 +6954,19 @@
         <v>47</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>35</v>
@@ -7015,7 +7015,7 @@
         <v>35</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
@@ -7033,30 +7033,30 @@
         <v>35</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>336</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7082,20 +7082,20 @@
         <v>66</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q42" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="P42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Q42" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="R42" t="s" s="2">
         <v>35</v>
@@ -7119,28 +7119,28 @@
         <v>115</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
@@ -7158,10 +7158,10 @@
         <v>35</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>35</v>
@@ -7178,10 +7178,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7204,17 +7204,17 @@
         <v>47</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>35</v>
@@ -7263,7 +7263,7 @@
         <v>35</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
@@ -7281,10 +7281,10 @@
         <v>35</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>35</v>
@@ -7301,10 +7301,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7330,14 +7330,14 @@
         <v>60</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>35</v>
@@ -7386,16 +7386,16 @@
         <v>35</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="AI44" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>58</v>
@@ -7404,10 +7404,10 @@
         <v>35</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>35</v>
@@ -7424,10 +7424,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7453,16 +7453,16 @@
         <v>66</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>35</v>
@@ -7511,7 +7511,7 @@
         <v>35</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -7529,10 +7529,10 @@
         <v>35</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>35</v>
@@ -7549,10 +7549,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7575,13 +7575,13 @@
         <v>47</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7632,7 +7632,7 @@
         <v>35</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -7647,13 +7647,13 @@
         <v>58</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>35</v>
@@ -7670,10 +7670,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7696,13 +7696,13 @@
         <v>35</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7753,7 +7753,7 @@
         <v>35</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -7774,7 +7774,7 @@
         <v>35</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>35</v>
@@ -7791,10 +7791,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7823,7 +7823,7 @@
         <v>93</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>95</v>
@@ -7876,7 +7876,7 @@
         <v>35</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -7897,7 +7897,7 @@
         <v>35</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>35</v>
@@ -7914,14 +7914,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7943,10 +7943,10 @@
         <v>92</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>95</v>
@@ -8001,7 +8001,7 @@
         <v>35</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -8039,10 +8039,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8068,10 +8068,10 @@
         <v>123</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8098,7 +8098,7 @@
         <v>35</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>135</v>
+        <v>384</v>
       </c>
       <c r="Y50" t="s" s="2">
         <v>385</v>
@@ -8122,7 +8122,7 @@
         <v>35</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -8430,13 +8430,13 @@
         <v>35</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8487,7 +8487,7 @@
         <v>35</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -8508,7 +8508,7 @@
         <v>35</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>35</v>
@@ -8557,7 +8557,7 @@
         <v>93</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>95</v>
@@ -8598,19 +8598,19 @@
         <v>35</v>
       </c>
       <c r="AB54" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE54" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AC54" t="s" s="2">
+      <c r="AF54" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -8631,7 +8631,7 @@
         <v>35</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>35</v>
@@ -8797,7 +8797,7 @@
         <v>47</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>416</v>
@@ -9072,7 +9072,7 @@
         <v>35</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>431</v>
@@ -9281,7 +9281,7 @@
         <v>47</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>440</v>
@@ -9439,7 +9439,7 @@
         <v>35</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="Y61" t="s" s="2">
         <v>448</v>
@@ -9527,7 +9527,7 @@
         <v>35</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>451</v>
@@ -9648,13 +9648,13 @@
         <v>35</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9705,7 +9705,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -9726,7 +9726,7 @@
         <v>35</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>35</v>
@@ -9775,7 +9775,7 @@
         <v>93</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>95</v>
@@ -9828,7 +9828,7 @@
         <v>35</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -9849,7 +9849,7 @@
         <v>35</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>35</v>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9895,10 +9895,10 @@
         <v>92</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>95</v>
@@ -9953,7 +9953,7 @@
         <v>35</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -10017,7 +10017,7 @@
         <v>35</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>458</v>
@@ -10259,7 +10259,7 @@
         <v>35</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>465</v>
@@ -10380,7 +10380,7 @@
         <v>35</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>469</v>
@@ -10534,7 +10534,7 @@
         <v>35</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="Y70" t="s" s="2">
         <v>475</v>
@@ -10655,7 +10655,7 @@
         <v>35</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="Y71" t="s" s="2">
         <v>481</v>
@@ -10743,7 +10743,7 @@
         <v>35</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>484</v>
@@ -10866,13 +10866,13 @@
         <v>35</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10923,7 +10923,7 @@
         <v>35</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -10944,7 +10944,7 @@
         <v>35</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>35</v>
@@ -10993,7 +10993,7 @@
         <v>93</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>95</v>
@@ -11046,7 +11046,7 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -11067,7 +11067,7 @@
         <v>35</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>35</v>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11113,10 +11113,10 @@
         <v>92</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>95</v>
@@ -11171,7 +11171,7 @@
         <v>35</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -11235,7 +11235,7 @@
         <v>35</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>493</v>
@@ -11313,7 +11313,7 @@
         <v>495</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>35</v>
@@ -11477,7 +11477,7 @@
         <v>35</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>504</v>
@@ -11598,7 +11598,7 @@
         <v>35</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>509</v>
@@ -11719,13 +11719,13 @@
         <v>35</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11776,7 +11776,7 @@
         <v>35</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>
@@ -11797,7 +11797,7 @@
         <v>35</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>35</v>
@@ -11846,7 +11846,7 @@
         <v>93</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>95</v>
@@ -11899,7 +11899,7 @@
         <v>35</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>36</v>
@@ -11920,7 +11920,7 @@
         <v>35</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>35</v>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11966,10 +11966,10 @@
         <v>92</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>95</v>
@@ -12024,7 +12024,7 @@
         <v>35</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
@@ -12088,7 +12088,7 @@
         <v>35</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>515</v>
@@ -12209,7 +12209,7 @@
         <v>35</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>518</v>
@@ -12363,7 +12363,7 @@
         <v>35</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="Y85" t="s" s="2">
         <v>523</v>
@@ -12498,14 +12498,14 @@
         <v>35</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AC86" s="2"/>
       <c r="AD86" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>525</v>
@@ -12574,7 +12574,7 @@
         <v>35</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>527</v>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3479" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3479" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -246,10 +246,10 @@
     <t>Mapping: CDA (R2)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -514,6 +514,10 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-6:297: fixed value "completed" {null}</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -523,10 +527,10 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>299: transform using "not-done" on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
+  </si>
+  <si>
     <t>Immun.Immunization.ImmunizationNameIEN</t>
-  </si>
-  <si>
-    <t>299: transform using "not-done" on V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - NAME (#9000010.11-.01 &gt; 9999999.14-.01) case text like 'contraindicated', 'refused', 'decline', 'not avail'</t>
   </si>
   <si>
     <t>Immunization.statusReason</t>
@@ -834,10 +838,10 @@
     <t>FiveWs.subject</t>
   </si>
   <si>
+    <t>333: source value from V IMMUNIZATION - PATIENT NAME (#9000010.11-.02)</t>
+  </si>
+  <si>
     <t>Immun.Immunization.PatientIEN</t>
-  </si>
-  <si>
-    <t>333: source value from V IMMUNIZATION - PATIENT NAME (#9000010.11-.02)</t>
   </si>
   <si>
     <t>Immunization.encounter</t>
@@ -910,12 +914,12 @@
 </t>
   </si>
   <si>
+    <t>334: source value from V IMMUNIZATION - EVENT DATE AND TIME (#9000010.11-1201)</t>
+  </si>
+  <si>
     <t>Immun.Immunization.EventDateTime</t>
   </si>
   <si>
-    <t>334: source value from V IMMUNIZATION - EVENT DATE AND TIME (#9000010.11-1201)</t>
-  </si>
-  <si>
     <t>Immunization.recorded</t>
   </si>
   <si>
@@ -955,10 +959,10 @@
     <t>FiveWs.source</t>
   </si>
   <si>
+    <t>607: transform using VF_immunizationPrimarySource on V IMMUNIZATION - EVENT INFORMATION SOURCE (#9000010.11-1301)</t>
+  </si>
+  <si>
     <t>Immun.Immunization.ImmunizationInformationSourceIEN</t>
-  </si>
-  <si>
-    <t>607: transform using VF_immunizationPrimarySource on V IMMUNIZATION - EVENT INFORMATION SOURCE (#9000010.11-1301)</t>
   </si>
   <si>
     <t>Immunization.reportOrigin</t>
@@ -1142,10 +1146,10 @@
     <t>.doseQuantity</t>
   </si>
   <si>
+    <t>464: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES- (#9000010.11-1313 &gt; 757.5-)</t>
+  </si>
+  <si>
     <t>Immun.Immunization.DoseUnit</t>
-  </si>
-  <si>
-    <t>464: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES- (#9000010.11-1313 &gt; 757.5-)</t>
   </si>
   <si>
     <t>Immunization.doseQuantity.id</t>
@@ -1182,10 +1186,10 @@
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
+    <t>340: source value from V IMMUNIZATION - DOSE (#9000010.11-1312)</t>
+  </si>
+  <si>
     <t>Immun.Immunization.Dosage</t>
-  </si>
-  <si>
-    <t>340: source value from V IMMUNIZATION - DOSE (#9000010.11-1312)</t>
   </si>
   <si>
     <t>Immunization.doseQuantity.comparator</t>
@@ -1376,10 +1380,10 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
+    <t>342: reference from V IMMUNIZATION - ENCOUNTER PROVIDER (#9000010.11-1204)</t>
+  </si>
+  <si>
     <t>Immun.Immunization.ImmunizingStaffIEN</t>
-  </si>
-  <si>
-    <t>342: reference from V IMMUNIZATION - ENCOUNTER PROVIDER (#9000010.11-1204)</t>
   </si>
   <si>
     <t>Immunization.note</t>
@@ -1466,10 +1470,10 @@
     <t>Act.text</t>
   </si>
   <si>
+    <t>343: source value from V IMMUNIZATION - COMMENTS (#9000010.11-81101)</t>
+  </si>
+  <si>
     <t>Immun.Immunization.ImmunizationComments</t>
-  </si>
-  <si>
-    <t>343: source value from V IMMUNIZATION - COMMENTS (#9000010.11-81101)</t>
   </si>
   <si>
     <t>Immunization.reasonCode</t>
@@ -1788,10 +1792,10 @@
     <t>doseNumberString</t>
   </si>
   <si>
+    <t>344: source value from V IMMUNIZATION - SERIES (#9000010.11-.04)</t>
+  </si>
+  <si>
     <t>Immun.Immunization.Series</t>
-  </si>
-  <si>
-    <t>344: source value from V IMMUNIZATION - SERIES (#9000010.11-.04)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -2160,8 +2164,8 @@
     <col min="39" max="39" width="236.8828125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="158.05078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="53.78515625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="191.34765625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="191.34765625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="53.78515625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3620,36 +3624,36 @@
         <v>78</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3672,16 +3676,16 @@
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3711,7 +3715,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3729,7 +3733,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3744,13 +3748,13 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>78</v>
@@ -3759,18 +3763,18 @@
         <v>78</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3793,13 +3797,13 @@
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3830,7 +3834,7 @@
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -3848,7 +3852,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>89</v>
@@ -3857,39 +3861,39 @@
         <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>184</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3912,13 +3916,13 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3969,7 +3973,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3990,7 +3994,7 @@
         <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -4007,10 +4011,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4039,7 +4043,7 @@
         <v>136</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>138</v>
@@ -4080,19 +4084,19 @@
         <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4113,7 +4117,7 @@
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -4130,10 +4134,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4156,19 +4160,19 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -4217,7 +4221,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4235,10 +4239,10 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -4255,10 +4259,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4281,13 +4285,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4338,7 +4342,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4359,7 +4363,7 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -4376,10 +4380,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4408,7 +4412,7 @@
         <v>136</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>138</v>
@@ -4449,19 +4453,19 @@
         <v>78</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4482,7 +4486,7 @@
         <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4499,10 +4503,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4528,16 +4532,16 @@
         <v>103</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4586,7 +4590,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4604,10 +4608,10 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -4624,10 +4628,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4650,16 +4654,16 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4709,7 +4713,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4727,10 +4731,10 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4747,10 +4751,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4776,14 +4780,14 @@
         <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -4832,7 +4836,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4850,10 +4854,10 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4862,18 +4866,18 @@
         <v>78</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>78</v>
+        <v>231</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4896,17 +4900,17 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4955,7 +4959,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4973,10 +4977,10 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4993,10 +4997,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5019,19 +5023,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -5080,7 +5084,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5098,10 +5102,10 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -5118,10 +5122,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5144,19 +5148,19 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5205,7 +5209,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5223,10 +5227,10 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -5243,14 +5247,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5269,13 +5273,13 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5326,7 +5330,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -5341,33 +5345,33 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5390,13 +5394,13 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5447,7 +5451,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5462,16 +5466,16 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>78</v>
@@ -5485,10 +5489,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5511,16 +5515,16 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5558,17 +5562,17 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>89</v>
@@ -5583,19 +5587,19 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>78</v>
@@ -5606,13 +5610,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>78</v>
@@ -5634,16 +5638,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5693,7 +5697,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>89</v>
@@ -5708,33 +5712,33 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5757,13 +5761,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5814,7 +5818,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5835,27 +5839,27 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>295</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5878,16 +5882,16 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5937,7 +5941,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5955,30 +5959,30 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6001,16 +6005,16 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6036,13 +6040,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -6060,7 +6064,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6078,13 +6082,13 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -6098,10 +6102,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6124,13 +6128,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6181,7 +6185,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6196,16 +6200,16 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -6219,10 +6223,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6245,13 +6249,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6302,7 +6306,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6320,30 +6324,30 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>78</v>
+        <v>329</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>328</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6366,13 +6370,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6423,7 +6427,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6441,30 +6445,30 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>335</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6487,13 +6491,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6544,7 +6548,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6562,10 +6566,10 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -6582,10 +6586,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6608,13 +6612,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6641,13 +6645,13 @@
         <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -6665,7 +6669,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6683,16 +6687,16 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>78</v>
@@ -6703,10 +6707,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6729,13 +6733,13 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6762,13 +6766,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6786,7 +6790,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6804,16 +6808,16 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>78</v>
@@ -6824,10 +6828,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6850,13 +6854,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6907,7 +6911,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6925,10 +6929,10 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6937,18 +6941,18 @@
         <v>78</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6971,13 +6975,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7028,7 +7032,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7049,7 +7053,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -7066,10 +7070,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7098,7 +7102,7 @@
         <v>136</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>138</v>
@@ -7139,19 +7143,19 @@
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7172,7 +7176,7 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -7189,10 +7193,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7215,19 +7219,19 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7276,7 +7280,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7294,10 +7298,10 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -7306,18 +7310,18 @@
         <v>78</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7343,20 +7347,20 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>78</v>
@@ -7380,10 +7384,10 @@
         <v>158</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -7401,7 +7405,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7419,10 +7423,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7439,10 +7443,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7465,17 +7469,17 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7524,7 +7528,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7542,10 +7546,10 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7562,10 +7566,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7591,14 +7595,14 @@
         <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7647,7 +7651,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7656,7 +7660,7 @@
         <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>101</v>
@@ -7665,10 +7669,10 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7685,10 +7689,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7714,16 +7718,16 @@
         <v>109</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7772,7 +7776,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7790,10 +7794,10 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7810,10 +7814,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7836,13 +7840,13 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7893,7 +7897,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7908,13 +7912,13 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7931,10 +7935,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7957,13 +7961,13 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8014,7 +8018,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8035,7 +8039,7 @@
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>78</v>
@@ -8052,10 +8056,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8084,7 +8088,7 @@
         <v>136</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>138</v>
@@ -8137,7 +8141,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8158,7 +8162,7 @@
         <v>78</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -8175,14 +8179,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8204,10 +8208,10 @@
         <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>138</v>
@@ -8262,7 +8266,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8300,10 +8304,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8326,13 +8330,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8359,13 +8363,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8383,7 +8387,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8398,13 +8402,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8421,10 +8425,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8447,16 +8451,16 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8506,7 +8510,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>89</v>
@@ -8521,33 +8525,33 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8570,13 +8574,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8627,7 +8631,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8642,13 +8646,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8665,10 +8669,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8691,13 +8695,13 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8748,7 +8752,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8769,7 +8773,7 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8786,10 +8790,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8818,7 +8822,7 @@
         <v>136</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>138</v>
@@ -8859,19 +8863,19 @@
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8892,7 +8896,7 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8909,10 +8913,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8935,16 +8939,16 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8994,7 +8998,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -9015,7 +9019,7 @@
         <v>132</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -9032,10 +9036,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9058,13 +9062,13 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9115,7 +9119,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9136,7 +9140,7 @@
         <v>132</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -9153,10 +9157,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9179,13 +9183,13 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9236,7 +9240,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>89</v>
@@ -9257,7 +9261,7 @@
         <v>132</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -9266,18 +9270,18 @@
         <v>78</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9300,13 +9304,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9333,13 +9337,13 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9357,7 +9361,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9372,13 +9376,13 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9395,10 +9399,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9421,13 +9425,13 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9478,7 +9482,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9493,7 +9497,7 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>78</v>
@@ -9516,10 +9520,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9542,23 +9546,23 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q61" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="R61" t="s" s="2">
         <v>78</v>
@@ -9603,7 +9607,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9621,7 +9625,7 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>132</v>
@@ -9641,10 +9645,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9667,13 +9671,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9700,13 +9704,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9724,7 +9728,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9762,10 +9766,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9788,13 +9792,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9845,7 +9849,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9857,7 +9861,7 @@
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -9883,10 +9887,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9909,13 +9913,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9966,7 +9970,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9987,7 +9991,7 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -10004,10 +10008,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10036,7 +10040,7 @@
         <v>136</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>138</v>
@@ -10089,7 +10093,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10110,7 +10114,7 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -10127,14 +10131,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10156,10 +10160,10 @@
         <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>138</v>
@@ -10214,7 +10218,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10252,10 +10256,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10278,13 +10282,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10335,7 +10339,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10353,7 +10357,7 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>132</v>
@@ -10373,10 +10377,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10402,10 +10406,10 @@
         <v>103</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10456,7 +10460,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10494,10 +10498,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10520,13 +10524,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10577,7 +10581,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10595,7 +10599,7 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>132</v>
@@ -10615,10 +10619,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10641,13 +10645,13 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10698,7 +10702,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10716,7 +10720,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>132</v>
@@ -10736,10 +10740,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10762,13 +10766,13 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10795,13 +10799,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10819,7 +10823,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10837,7 +10841,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>132</v>
@@ -10857,10 +10861,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10883,13 +10887,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10916,13 +10920,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10940,7 +10944,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10978,10 +10982,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11004,16 +11008,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11063,7 +11067,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11081,10 +11085,10 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -11101,10 +11105,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11127,13 +11131,13 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11184,7 +11188,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11205,7 +11209,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -11222,10 +11226,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11254,7 +11258,7 @@
         <v>136</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>138</v>
@@ -11307,7 +11311,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11328,7 +11332,7 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11345,14 +11349,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11374,10 +11378,10 @@
         <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>138</v>
@@ -11432,7 +11436,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11470,10 +11474,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11496,13 +11500,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11553,7 +11557,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11571,10 +11575,10 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11591,10 +11595,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11617,13 +11621,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11674,7 +11678,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11692,10 +11696,10 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11704,18 +11708,18 @@
         <v>78</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>78</v>
+        <v>546</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>545</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11738,13 +11742,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11795,7 +11799,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11813,10 +11817,10 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11833,10 +11837,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11859,13 +11863,13 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11916,7 +11920,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11954,10 +11958,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11980,13 +11984,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12037,7 +12041,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12058,7 +12062,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -12075,10 +12079,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12107,7 +12111,7 @@
         <v>136</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>138</v>
@@ -12160,7 +12164,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12181,7 +12185,7 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -12198,14 +12202,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12227,10 +12231,10 @@
         <v>135</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>138</v>
@@ -12285,7 +12289,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12323,10 +12327,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12349,13 +12353,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12406,7 +12410,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12444,10 +12448,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12470,13 +12474,13 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12527,7 +12531,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12565,10 +12569,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12591,13 +12595,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12624,13 +12628,13 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -12648,7 +12652,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12686,10 +12690,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12712,16 +12716,16 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12759,17 +12763,17 @@
         <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>89</v>
@@ -12807,13 +12811,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
@@ -12835,16 +12839,16 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12894,7 +12898,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>89</v>
@@ -12924,18 +12928,18 @@
         <v>78</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12958,16 +12962,16 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13017,7 +13021,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,7 +515,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-6:297: fixed value "completed" {null}</t>
+inv-7:297: fixed value = completed if V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (#9000010.11-.01 &gt; 9999999.14-.03) case CVX populated {null}</t>
   </si>
   <si>
     <t>Event.status</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,7 +515,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-7:297: fixed value = completed if V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (#9000010.11-.01 &gt; 9999999.14-.03) case CVX populated {null}</t>
+inv-8:297: fixed value = completed if V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (#9000010.11-.01 &gt; 9999999.14-.03) case CVX populated {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1146,7 +1146,7 @@
     <t>.doseQuantity</t>
   </si>
   <si>
-    <t>464: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES- (#9000010.11-1313 &gt; 757.5-)</t>
+    <t>464: source value from V IMMUNIZATION - DOSE UNITS &gt; UCUM CODES - (#9000010.11-1313 &gt; 757.5-)</t>
   </si>
   <si>
     <t>Immun.Immunization.DoseUnit</t>
@@ -1701,7 +1701,7 @@
     <t>.value</t>
   </si>
   <si>
-    <t>++: reference from V IMMUNIZATION - REACTION (#9000010.11-.06)</t>
+    <t>++: reference from null (#null)</t>
   </si>
   <si>
     <t>Immunization.reaction.reported</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1701,7 +1701,7 @@
     <t>.value</t>
   </si>
   <si>
-    <t>++: reference from null (#null)</t>
+    <t>++: reference</t>
   </si>
   <si>
     <t>Immunization.reaction.reported</t>

--- a/docs/StructureDefinition-Immunization.xlsx
+++ b/docs/StructureDefinition-Immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA V IMMUNIZATION (file 9000010.11) to FHIR Immunization</t>
+    <t>This StructureDefinition contains the maps for VistA file V IMMUNIZATION (#9000010.11) to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -515,7 +515,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-8:297: fixed value = completed if V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (#9000010.11-.01 &gt; 9999999.14-.03) case CVX populated {null}</t>
+inv-8:297: fixed value = completed when V IMMUNIZATION - IMMUNIZATION &gt; IMMUNIZATION - CVX CODE (#9000010.11-.01 &gt; 9999999.14-.03) case CVX populated {null}</t>
   </si>
   <si>
     <t>Event.status</t>
